--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487547_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487547_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.2412</v>
+        <v>2.2433</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8108</v>
+        <v>0.3586</v>
       </c>
       <c r="F2" t="n">
-        <v>1.4303</v>
+        <v>1.8848</v>
       </c>
       <c r="G2" t="n">
         <v>-0.2432</v>
@@ -610,13 +610,13 @@
         <v>0.7834</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.0664</v>
+        <v>-0.0643</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1764</v>
+        <v>-0.2758</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2428</v>
+        <v>0.2116</v>
       </c>
       <c r="V2" t="n">
         <v>1.7673</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.8754</v>
+        <v>1.2789</v>
       </c>
       <c r="E3" t="n">
-        <v>3.0001</v>
+        <v>2.5908</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.1248</v>
+        <v>-1.3119</v>
       </c>
       <c r="G3" t="n">
         <v>-0.4271</v>
@@ -688,13 +688,13 @@
         <v>1.3709</v>
       </c>
       <c r="S3" t="n">
-        <v>1.1274</v>
+        <v>0.5309</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1941</v>
+        <v>-0.2153</v>
       </c>
       <c r="U3" t="n">
-        <v>0.9333</v>
+        <v>0.7462</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6967</v>
+        <v>0.7769</v>
       </c>
       <c r="E4" t="n">
         <v>-0.1578</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8545</v>
+        <v>0.9347</v>
       </c>
       <c r="G4" t="n">
         <v>0.4298</v>
@@ -766,13 +766,13 @@
         <v>0.3917</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1247</v>
+        <v>-0.0446</v>
       </c>
       <c r="T4" t="n">
         <v>-0.1782</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0535</v>
+        <v>0.1337</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.264</v>
+        <v>0.7419</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.312</v>
+        <v>-0.048</v>
       </c>
       <c r="F5" t="n">
-        <v>0.576</v>
+        <v>0.7899</v>
       </c>
       <c r="G5" t="n">
         <v>0.7507</v>
@@ -844,13 +844,13 @@
         <v>0.3917</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.8784</v>
+        <v>-0.4005</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7722</v>
+        <v>-0.5082</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1062</v>
+        <v>0.1076</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.9066</v>
+        <v>-0.524</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6647999999999999</v>
+        <v>1.0741</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.5714</v>
+        <v>-1.5981</v>
       </c>
       <c r="G6" t="n">
         <v>-1.969</v>
@@ -922,13 +922,13 @@
         <v>1.1751</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1543</v>
+        <v>0.2283</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5764</v>
+        <v>-0.167</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4221</v>
+        <v>0.3954</v>
       </c>
       <c r="V6" t="n">
         <v>1.2166</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.2308</v>
+        <v>-1.0385</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.5123</v>
+        <v>-2.8389</v>
       </c>
       <c r="F7" t="n">
-        <v>2.2815</v>
+        <v>1.8004</v>
       </c>
       <c r="G7" t="n">
         <v>-3.3904</v>
@@ -1000,13 +1000,13 @@
         <v>1.7626</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1537</v>
+        <v>0.0385</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.6633</v>
+        <v>-0.9898</v>
       </c>
       <c r="U7" t="n">
-        <v>1.5095</v>
+        <v>1.0284</v>
       </c>
       <c r="V7" t="n">
         <v>0.5507</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.2924</v>
+        <v>-1.8588</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.33</v>
+        <v>-0.2706</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.9624</v>
+        <v>-1.5882</v>
       </c>
       <c r="G8" t="n">
         <v>-0.8771</v>
@@ -1078,13 +1078,13 @@
         <v>1.3709</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.648</v>
+        <v>-0.2144</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6246</v>
+        <v>-0.5652</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0234</v>
+        <v>0.3508</v>
       </c>
       <c r="V8" t="n">
         <v>-1.159</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>C. VARELA ROMERO</t>
+          <t>M. GARCIA FRAGA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.3006</v>
+        <v>-2.2432</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.6411</v>
+        <v>-1.0023</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3405</v>
+        <v>-1.2409</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.9529</v>
+        <v>-2.8809</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.2848</v>
+        <v>-0.0871</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.6681</v>
+        <v>-2.7938</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4012</v>
+        <v>0.08459999999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>1.3422</v>
+        <v>1.4086</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.9409999999999999</v>
+        <v>-1.3241</v>
       </c>
       <c r="M9" t="n">
-        <v>-3.3541</v>
+        <v>-2.9655</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.627</v>
+        <v>-1.4957</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.7271</v>
+        <v>-1.4698</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.3709</v>
+        <v>0.3917</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.1336</v>
+        <v>-0.9792</v>
       </c>
       <c r="R9" t="n">
-        <v>1.7626</v>
+        <v>1.3709</v>
       </c>
       <c r="S9" t="n">
-        <v>1.1396</v>
+        <v>0.246</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4593</v>
+        <v>-0.1076</v>
       </c>
       <c r="U9" t="n">
-        <v>1.599</v>
+        <v>0.3536</v>
       </c>
       <c r="V9" t="n">
-        <v>0.8837</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5507</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0.3329</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>G. SABATER MARTINEZ</t>
+          <t>C. VARELA ROMERO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.4374</v>
+        <v>-3.0072</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.9409</v>
+        <v>-2.7863</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5034999999999999</v>
+        <v>-0.2209</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.5173</v>
+        <v>-2.9529</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1912</v>
+        <v>-0.2848</v>
       </c>
       <c r="I10" t="n">
-        <v>-3.7085</v>
+        <v>-2.6681</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.5747</v>
+        <v>0.4012</v>
       </c>
       <c r="K10" t="n">
-        <v>1.0735</v>
+        <v>1.3422</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.6481</v>
+        <v>-0.9409999999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.9427</v>
+        <v>-3.3541</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.8822</v>
+        <v>-1.627</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.0604</v>
+        <v>-1.7271</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.3917</v>
+        <v>-1.3709</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.1543</v>
+        <v>-3.1336</v>
       </c>
       <c r="R10" t="n">
         <v>1.7626</v>
       </c>
       <c r="S10" t="n">
-        <v>1.4716</v>
+        <v>0.433</v>
       </c>
       <c r="T10" t="n">
-        <v>0.7881</v>
+        <v>-0.6046</v>
       </c>
       <c r="U10" t="n">
-        <v>0.6835</v>
+        <v>1.0376</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.8837</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.5507</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>0.3329</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. GARCIA FRAGA</t>
+          <t>M. TOMIC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,58 +1267,58 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.7328</v>
+        <v>-3.2301</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.4116</v>
+        <v>-3.0853</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.3211</v>
+        <v>-0.1448</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.8809</v>
+        <v>-1.4791</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.0871</v>
+        <v>-1.6611</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.7938</v>
+        <v>0.1821</v>
       </c>
       <c r="J11" t="n">
-        <v>0.08459999999999999</v>
+        <v>-0.601</v>
       </c>
       <c r="K11" t="n">
-        <v>1.4086</v>
+        <v>-0.6414</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.3241</v>
+        <v>0.0404</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.9655</v>
+        <v>-0.8781</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.4957</v>
+        <v>-1.0197</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.4698</v>
+        <v>0.1416</v>
       </c>
       <c r="P11" t="n">
-        <v>0.3917</v>
+        <v>-1.5668</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9792</v>
+        <v>-2.1543</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3709</v>
+        <v>0.5875</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2435</v>
+        <v>-0.1842</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.517</v>
+        <v>-0.3299</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2734</v>
+        <v>0.1457</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M. TOMIC</t>
+          <t>G. SABATER MARTINEZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,58 +1345,58 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.5684</v>
+        <v>-3.234</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.2899</v>
+        <v>-3.6572</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2785</v>
+        <v>0.4233</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.4791</v>
+        <v>-3.5173</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.6611</v>
+        <v>0.1912</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1821</v>
+        <v>-3.7085</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.601</v>
+        <v>-1.5747</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.6414</v>
+        <v>1.0735</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0404</v>
+        <v>-2.6481</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.8781</v>
+        <v>-1.9427</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.0197</v>
+        <v>-0.8822</v>
       </c>
       <c r="O12" t="n">
-        <v>0.1416</v>
+        <v>-1.0604</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.5668</v>
+        <v>-0.3917</v>
       </c>
       <c r="Q12" t="n">
         <v>-2.1543</v>
       </c>
       <c r="R12" t="n">
-        <v>0.5875</v>
+        <v>1.7626</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5226</v>
+        <v>0.675</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5346</v>
+        <v>0.0717</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0121</v>
+        <v>0.6032999999999999</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-10.3917</v>
+        <v>-10.0948</v>
       </c>
       <c r="E13" t="n">
-        <v>-10.1199</v>
+        <v>-9.822900000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.2719000000000003</v>
+        <v>-0.2716999999999999</v>
       </c>
       <c r="G13" t="n">
         <v>-16.5565</v>
@@ -1444,7 +1444,7 @@
         <v>0.1827000000000005</v>
       </c>
       <c r="K13" t="n">
-        <v>8.473299999999998</v>
+        <v>8.4733</v>
       </c>
       <c r="L13" t="n">
         <v>-8.290699999999999</v>
@@ -1456,7 +1456,7 @@
         <v>-9.4941</v>
       </c>
       <c r="O13" t="n">
-        <v>-7.245</v>
+        <v>-7.244999999999999</v>
       </c>
       <c r="P13" t="n">
         <v>1.9585</v>
@@ -1468,13 +1468,13 @@
         <v>12.7299</v>
       </c>
       <c r="S13" t="n">
-        <v>0.9470000000000001</v>
+        <v>1.2437</v>
       </c>
       <c r="T13" t="n">
-        <v>-4.167</v>
+        <v>-3.8699</v>
       </c>
       <c r="U13" t="n">
-        <v>5.114</v>
+        <v>5.1139</v>
       </c>
       <c r="V13" t="n">
         <v>3.2593</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.7902</v>
+        <v>5.2785</v>
       </c>
       <c r="E14" t="n">
-        <v>3.1435</v>
+        <v>2.6319</v>
       </c>
       <c r="F14" t="n">
         <v>2.6467</v>
@@ -1546,10 +1546,10 @@
         <v>1.7626</v>
       </c>
       <c r="S14" t="n">
-        <v>0.7834</v>
+        <v>0.2717</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0576</v>
+        <v>-0.454</v>
       </c>
       <c r="U14" t="n">
         <v>0.7258</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.788</v>
+        <v>4.2001</v>
       </c>
       <c r="E15" t="n">
-        <v>1.9685</v>
+        <v>2.3778</v>
       </c>
       <c r="F15" t="n">
-        <v>1.8196</v>
+        <v>1.8223</v>
       </c>
       <c r="G15" t="n">
         <v>7.1898</v>
@@ -1624,13 +1624,13 @@
         <v>0.9792</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.4261</v>
+        <v>-0.014</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.2474</v>
+        <v>-0.8381</v>
       </c>
       <c r="U15" t="n">
-        <v>0.8213</v>
+        <v>0.8241000000000001</v>
       </c>
       <c r="V15" t="n">
         <v>0.9412</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.6657</v>
+        <v>3.7174</v>
       </c>
       <c r="E16" t="n">
-        <v>1.203</v>
+        <v>1.3053</v>
       </c>
       <c r="F16" t="n">
-        <v>2.4628</v>
+        <v>2.4121</v>
       </c>
       <c r="G16" t="n">
         <v>3.9343</v>
@@ -1702,13 +1702,13 @@
         <v>1.1751</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4265</v>
+        <v>-0.3748</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.8316</v>
+        <v>-0.7292999999999999</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4052</v>
+        <v>0.3545</v>
       </c>
       <c r="V16" t="n">
         <v>0.9412</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.5407</v>
+        <v>2.9279</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.3883</v>
+        <v>-0.0813</v>
       </c>
       <c r="F17" t="n">
-        <v>2.9289</v>
+        <v>3.0091</v>
       </c>
       <c r="G17" t="n">
         <v>1.0745</v>
@@ -1780,13 +1780,13 @@
         <v>1.5668</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1006</v>
+        <v>0.2866</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7722</v>
+        <v>-0.4652</v>
       </c>
       <c r="U17" t="n">
-        <v>0.6716</v>
+        <v>0.7518</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.3528</v>
+        <v>1.7253</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.2942</v>
+        <v>-0.1919</v>
       </c>
       <c r="F18" t="n">
-        <v>1.6471</v>
+        <v>1.9172</v>
       </c>
       <c r="G18" t="n">
         <v>0.2427</v>
@@ -1858,13 +1858,13 @@
         <v>1.1751</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.065</v>
+        <v>0.3074</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4464</v>
+        <v>-0.3441</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3814</v>
+        <v>0.6515</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. SABUGUEIRO ABEIJÓN</t>
+          <t>A. KOVAC MARTINEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5545</v>
+        <v>0.643</v>
       </c>
       <c r="E19" t="n">
-        <v>1.6743</v>
+        <v>-0.9156</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.1197</v>
+        <v>1.5586</v>
       </c>
       <c r="G19" t="n">
-        <v>1.2037</v>
+        <v>2.4776</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.0796</v>
+        <v>0.8153</v>
       </c>
       <c r="I19" t="n">
-        <v>1.2833</v>
+        <v>1.6622</v>
       </c>
       <c r="J19" t="n">
-        <v>1.4672</v>
+        <v>1.7787</v>
       </c>
       <c r="K19" t="n">
-        <v>0.7349</v>
+        <v>1.082</v>
       </c>
       <c r="L19" t="n">
-        <v>0.7323</v>
+        <v>0.6967</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.2635</v>
+        <v>0.6989</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.8145</v>
+        <v>-0.2667</v>
       </c>
       <c r="O19" t="n">
-        <v>0.551</v>
+        <v>0.9655</v>
       </c>
       <c r="P19" t="n">
-        <v>0.5875</v>
+        <v>-1.5668</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.9585</v>
       </c>
       <c r="R19" t="n">
-        <v>0.5875</v>
+        <v>0.3917</v>
       </c>
       <c r="S19" t="n">
-        <v>0.2553</v>
+        <v>0.0076</v>
       </c>
       <c r="T19" t="n">
-        <v>0.207</v>
+        <v>-0.7358</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0482</v>
+        <v>0.7433999999999999</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.492</v>
+        <v>-0.2754</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.492</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. KOVAC MARTINEZ</t>
+          <t>P. SABUGUEIRO ABEIJÓN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.112</v>
+        <v>0.4863</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.4272</v>
+        <v>1.4696</v>
       </c>
       <c r="F20" t="n">
-        <v>1.3152</v>
+        <v>-0.9833</v>
       </c>
       <c r="G20" t="n">
-        <v>2.4776</v>
+        <v>1.2037</v>
       </c>
       <c r="H20" t="n">
-        <v>0.8153</v>
+        <v>-0.0796</v>
       </c>
       <c r="I20" t="n">
-        <v>1.6622</v>
+        <v>1.2833</v>
       </c>
       <c r="J20" t="n">
-        <v>1.7787</v>
+        <v>1.4672</v>
       </c>
       <c r="K20" t="n">
-        <v>1.082</v>
+        <v>0.7349</v>
       </c>
       <c r="L20" t="n">
-        <v>0.6967</v>
+        <v>0.7323</v>
       </c>
       <c r="M20" t="n">
-        <v>0.6989</v>
+        <v>-0.2635</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.2667</v>
+        <v>-0.8145</v>
       </c>
       <c r="O20" t="n">
-        <v>0.9655</v>
+        <v>0.551</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.5668</v>
+        <v>0.5875</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9585</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.3917</v>
+        <v>0.5875</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7474</v>
+        <v>0.187</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.2474</v>
+        <v>0.0023</v>
       </c>
       <c r="U20" t="n">
-        <v>0.5</v>
+        <v>0.1847</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.2754</v>
+        <v>-1.492</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.2754</v>
+        <v>-1.492</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.1849</v>
+        <v>-1.6745</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.657</v>
+        <v>-1.0663</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.5279</v>
+        <v>-0.6081</v>
       </c>
       <c r="G21" t="n">
         <v>0.0081</v>
@@ -2092,13 +2092,13 @@
         <v>1.5668</v>
       </c>
       <c r="S21" t="n">
-        <v>0.4153</v>
+        <v>-0.0743</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1476</v>
+        <v>-0.2617</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2677</v>
+        <v>0.1875</v>
       </c>
       <c r="V21" t="n">
         <v>-1.2166</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.9207</v>
+        <v>-2.3835</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.6717</v>
+        <v>-2.0811</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.249</v>
+        <v>-0.3025</v>
       </c>
       <c r="G22" t="n">
         <v>-1.1991</v>
@@ -2170,13 +2170,13 @@
         <v>0.3917</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1721</v>
+        <v>-0.6349</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2682</v>
+        <v>-0.6775</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0961</v>
+        <v>0.0426</v>
       </c>
       <c r="V22" t="n">
         <v>-0.9412</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.0825</v>
+        <v>-3.8465</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.2789</v>
+        <v>-3.1765</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.8036</v>
+        <v>-0.67</v>
       </c>
       <c r="G23" t="n">
         <v>-3.3025</v>
@@ -2248,13 +2248,13 @@
         <v>1.1751</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4632</v>
+        <v>-0.2272</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7128</v>
+        <v>-0.6105</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2497</v>
+        <v>0.3833</v>
       </c>
       <c r="V23" t="n">
         <v>-1.492</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>10.3918</v>
+        <v>11.074</v>
       </c>
       <c r="E24" t="n">
-        <v>0.2719999999999998</v>
+        <v>0.2719000000000005</v>
       </c>
       <c r="F24" t="n">
-        <v>10.1201</v>
+        <v>10.8021</v>
       </c>
       <c r="G24" t="n">
         <v>16.5564</v>
@@ -2308,7 +2308,7 @@
         <v>7.245100000000001</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.1826</v>
+        <v>-0.1826000000000002</v>
       </c>
       <c r="N24" t="n">
         <v>-8.4733</v>
@@ -2326,22 +2326,22 @@
         <v>10.7716</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.9468999999999999</v>
+        <v>-0.2649000000000001</v>
       </c>
       <c r="T24" t="n">
-        <v>-5.1138</v>
+        <v>-5.1139</v>
       </c>
       <c r="U24" t="n">
-        <v>4.167</v>
+        <v>4.8492</v>
       </c>
       <c r="V24" t="n">
-        <v>-3.2594</v>
+        <v>-3.259399999999999</v>
       </c>
       <c r="W24" t="n">
         <v>1.3769</v>
       </c>
       <c r="X24" t="n">
-        <v>-4.6362</v>
+        <v>-4.636199999999999</v>
       </c>
     </row>
   </sheetData>
